--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47ED888E-5316-47A9-9AD7-FD32E0B4DA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0148F895-807A-464E-8049-532044922FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -190,9 +199,6 @@
     <t>prince chaudhary</t>
   </si>
   <si>
-    <t>mca</t>
-  </si>
-  <si>
     <t>august</t>
   </si>
   <si>
@@ -200,6 +206,9 @@
   </si>
   <si>
     <t>felt little tired after alst class</t>
+  </si>
+  <si>
+    <t>MCA</t>
   </si>
 </sst>
 </file>
@@ -904,7 +913,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -912,7 +921,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -980,7 +989,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="9">
         <v>480</v>
@@ -1020,7 +1029,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1037,7 +1046,7 @@
         <v/>
       </c>
       <c r="J7" s="15" t="str">
-        <f t="shared" ref="J6:J69" si="1">IF(I7="","",1440-I7)</f>
+        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
         <v/>
       </c>
       <c r="K7" s="16"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0148F895-807A-464E-8049-532044922FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B76FE6-C8B2-4E9C-8485-85E38E420BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>MCA</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>feeling is not so great</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1033,26 +1045,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="14">
+        <v>450</v>
+      </c>
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>250</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>40</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B76FE6-C8B2-4E9C-8485-85E38E420BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFBFD10-DF4B-4294-AD8E-78078BC6220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,18 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>this day was very good</t>
   </si>
 </sst>
 </file>
@@ -1091,26 +1103,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="14">
+        <v>500</v>
+      </c>
+      <c r="C8" s="14">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14">
+        <v>200</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>400</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFBFD10-DF4B-4294-AD8E-78078BC6220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEC6BAC-7D1A-43A2-B357-5AD8191B47B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>this day was very good</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it was a nice day </t>
   </si>
 </sst>
 </file>
@@ -1149,26 +1155,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="14">
+        <v>500</v>
+      </c>
+      <c r="C9" s="14">
+        <v>50</v>
+      </c>
+      <c r="D9" s="14">
+        <v>200</v>
+      </c>
+      <c r="E9" s="14">
+        <v>70</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>300</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEC6BAC-7D1A-43A2-B357-5AD8191B47B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B23C94D-3D9E-4264-A31F-89B324BD1363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t xml:space="preserve">it was a nice day </t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>this was just a normal day</t>
   </si>
 </sst>
 </file>
@@ -1201,26 +1207,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14">
+        <v>200</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>200</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B23C94D-3D9E-4264-A31F-89B324BD1363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A1E6DF-559C-4D76-9571-CC5DBA5124DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,6 +246,12 @@
   <si>
     <t>this was just a normal day</t>
   </si>
+  <si>
+    <t xml:space="preserve">not very great day just average </t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -254,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +339,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1253,48 +1265,96 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46031</v>
+      </c>
+      <c r="B11" s="14">
+        <v>450</v>
+      </c>
+      <c r="C11" s="14">
+        <v>40</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>220</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46031</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>160</v>
+      </c>
+      <c r="E12" s="14">
+        <v>100</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>200</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
@@ -9863,6 +9923,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="J6:J401">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A1E6DF-559C-4D76-9571-CC5DBA5124DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B455133F-996E-4157-A702-CE0B0AFBB1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,9 +211,6 @@
     <t>MCA</t>
   </si>
   <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
     <t>feeling is not so great</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
   </si>
   <si>
     <t>Low</t>
-  </si>
-  <si>
-    <t>29/08/2026</t>
   </si>
   <si>
     <t>Excellent</t>
@@ -235,13 +229,7 @@
     <t>this day was very good</t>
   </si>
   <si>
-    <t>30/08/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">it was a nice day </t>
-  </si>
-  <si>
-    <t>31/08/2026</t>
   </si>
   <si>
     <t>this was just a normal day</t>
@@ -251,6 +239,33 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>2026/31/08</t>
+  </si>
+  <si>
+    <t>2026/30/08</t>
+  </si>
+  <si>
+    <t>2026/29/08</t>
+  </si>
+  <si>
+    <t>2026/28/08</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">just average </t>
+  </si>
+  <si>
+    <t xml:space="preserve">average </t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>high</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1097,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B7" s="14">
         <v>450</v>
@@ -1114,21 +1129,21 @@
         <v>500</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N7" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B8" s="14">
         <v>500</v>
@@ -1160,21 +1175,21 @@
         <v>260</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B9" s="14">
         <v>500</v>
@@ -1206,16 +1221,16 @@
         <v>320</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1255,13 +1270,13 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1307,12 +1322,12 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46031</v>
+        <v>46062</v>
       </c>
       <c r="B12" s="14">
         <v>480</v>
@@ -1344,61 +1359,109 @@
         <v>150</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46090</v>
+      </c>
+      <c r="B13" s="14">
+        <v>500</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46121</v>
+      </c>
+      <c r="B14" s="14">
+        <v>400</v>
+      </c>
+      <c r="C14" s="14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="14">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>160</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B455133F-996E-4157-A702-CE0B0AFBB1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76A968E-146F-4EA2-9EA7-88FC31171CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>high</t>
+  </si>
+  <si>
+    <t>felling tired</t>
   </si>
 </sst>
 </file>
@@ -1464,26 +1467,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46212</v>
+      </c>
+      <c r="B15" s="14">
+        <v>450</v>
+      </c>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
+      <c r="D15" s="14">
+        <v>200</v>
+      </c>
+      <c r="E15" s="14">
+        <v>160</v>
+      </c>
+      <c r="F15" s="14">
+        <v>280</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>150</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76A968E-146F-4EA2-9EA7-88FC31171CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66ACBD4-FC61-4B7A-96E5-19D34ECBF0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,12 @@
   </si>
   <si>
     <t>felling tired</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>low</t>
   </si>
 </sst>
 </file>
@@ -1513,26 +1519,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B16" s="14">
+        <v>460</v>
+      </c>
+      <c r="C16" s="14">
+        <v>70</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>200</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66ACBD4-FC61-4B7A-96E5-19D34ECBF0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D759C555-E6E5-4DDA-B159-99A9B213909E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>low</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1565,26 +1568,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B17" s="14">
+        <v>465</v>
+      </c>
+      <c r="C17" s="14">
+        <v>75</v>
+      </c>
+      <c r="D17" s="14">
+        <v>239</v>
+      </c>
+      <c r="E17" s="14">
+        <v>45</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>130</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1254</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>186</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D759C555-E6E5-4DDA-B159-99A9B213909E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A305D0AF-1763-47A9-AE93-6BE4D2C2E144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>everything was good</t>
   </si>
 </sst>
 </file>
@@ -1569,7 +1572,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46244</v>
+        <v>46274</v>
       </c>
       <c r="B17" s="14">
         <v>465</v>
@@ -1614,26 +1617,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B18" s="14">
+        <v>470</v>
+      </c>
+      <c r="C18" s="14">
+        <v>100</v>
+      </c>
+      <c r="D18" s="14">
+        <v>200</v>
+      </c>
+      <c r="E18" s="14">
+        <v>70</v>
+      </c>
+      <c r="F18" s="14">
+        <v>150</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>200</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A305D0AF-1763-47A9-AE93-6BE4D2C2E144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C934D-F313-4FA9-9635-25E161844FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1663,26 +1663,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46335</v>
+      </c>
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>50</v>
+      </c>
+      <c r="D19" s="14">
+        <v>300</v>
+      </c>
+      <c r="E19" s="14">
+        <v>100</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>100</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C934D-F313-4FA9-9635-25E161844FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5574E5CC-BB3A-4B0F-A2A9-DDB9FB7101FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>everything was good</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1709,26 +1712,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46365</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>100</v>
+      </c>
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>300</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5574E5CC-BB3A-4B0F-A2A9-DDB9FB7101FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8A0342-CC3C-4290-A17B-4F11D0D857EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,15 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>2026/14/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good </t>
+  </si>
+  <si>
+    <t>average day</t>
   </si>
 </sst>
 </file>
@@ -1758,26 +1767,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="14">
+        <v>450</v>
+      </c>
+      <c r="C21" s="14">
+        <v>50</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>100</v>
+      </c>
+      <c r="F21" s="14">
+        <v>6</v>
+      </c>
+      <c r="G21" s="14">
+        <v>300</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1006</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>434</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8A0342-CC3C-4290-A17B-4F11D0D857EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C9F258-DD35-4748-87CA-CCEA6898420A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>average day</t>
+  </si>
+  <si>
+    <t>2026/15/09</t>
   </si>
 </sst>
 </file>
@@ -1783,21 +1786,21 @@
         <v>100</v>
       </c>
       <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
         <v>6</v>
-      </c>
-      <c r="G21" s="14">
-        <v>300</v>
       </c>
       <c r="H21" s="14">
         <v>200</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1006</v>
+        <v>1300</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>434</v>
+        <v>140</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>84</v>
@@ -1813,26 +1816,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="14">
+        <v>445</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>150</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>250</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1405</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C9F258-DD35-4748-87CA-CCEA6898420A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCC06BA-3B9F-4511-A739-2F585FA3A8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>2026/15/09</t>
+  </si>
+  <si>
+    <t>2026/16/09</t>
   </si>
 </sst>
 </file>
@@ -1862,26 +1865,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="14">
+        <v>440</v>
+      </c>
+      <c r="C23" s="14">
+        <v>70</v>
+      </c>
+      <c r="D23" s="14">
+        <v>250</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>200</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCC06BA-3B9F-4511-A739-2F585FA3A8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6AAB69-84CA-4408-8AC4-4F1DB946A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>2026/16/09</t>
+  </si>
+  <si>
+    <t>2026/17/09</t>
   </si>
 </sst>
 </file>
@@ -1911,26 +1914,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>80</v>
+      </c>
+      <c r="D24" s="14">
+        <v>200</v>
+      </c>
+      <c r="E24" s="14">
+        <v>100</v>
+      </c>
+      <c r="F24" s="14">
+        <v>150</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6AAB69-84CA-4408-8AC4-4F1DB946A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94384A24-3CCD-4264-9C25-7F47DACDBA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>2026/17/09</t>
+  </si>
+  <si>
+    <t>2026/18/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling little bit tired </t>
   </si>
 </sst>
 </file>
@@ -1960,26 +1966,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>90</v>
+      </c>
+      <c r="D25" s="14">
+        <v>150</v>
+      </c>
+      <c r="E25" s="14">
+        <v>100</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>200</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94384A24-3CCD-4264-9C25-7F47DACDBA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF410A16-5BF3-4623-B1C8-5D373D565C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t xml:space="preserve">feeling little bit tired </t>
+  </si>
+  <si>
+    <t>2026/21/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not so much excited just normal </t>
   </si>
 </sst>
 </file>
@@ -2012,26 +2018,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="14">
+        <v>500</v>
+      </c>
+      <c r="C26" s="14">
+        <v>100</v>
+      </c>
+      <c r="D26" s="14">
+        <v>150</v>
+      </c>
+      <c r="E26" s="14">
+        <v>80</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>150</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF410A16-5BF3-4623-B1C8-5D373D565C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477D46FF-488B-4462-BB32-2BF1B70D4886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t xml:space="preserve">not so much excited just normal </t>
+  </si>
+  <si>
+    <t>2026//22/09</t>
   </si>
 </sst>
 </file>
@@ -2064,26 +2067,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>90</v>
+      </c>
+      <c r="D27" s="14">
+        <v>160</v>
+      </c>
+      <c r="E27" s="14">
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>180</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477D46FF-488B-4462-BB32-2BF1B70D4886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F024F18-4C28-483D-AAD9-B99052133A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>2026//22/09</t>
+  </si>
+  <si>
+    <t>2026/23/09</t>
+  </si>
+  <si>
+    <t>nothing speacial</t>
   </si>
 </sst>
 </file>
@@ -2113,26 +2119,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="14">
+        <v>470</v>
+      </c>
+      <c r="C28" s="14">
+        <v>100</v>
+      </c>
+      <c r="D28" s="14">
+        <v>160</v>
+      </c>
+      <c r="E28" s="14">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>150</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F024F18-4C28-483D-AAD9-B99052133A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0681A4-0A1B-4129-91C5-B2F41D90240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>nothing speacial</t>
+  </si>
+  <si>
+    <t>2026/24/09</t>
+  </si>
+  <si>
+    <t>it was a average day</t>
   </si>
 </sst>
 </file>
@@ -2165,26 +2171,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="14">
+        <v>465</v>
+      </c>
+      <c r="C29" s="14">
+        <v>90</v>
+      </c>
+      <c r="D29" s="14">
+        <v>170</v>
+      </c>
+      <c r="E29" s="14">
+        <v>110</v>
+      </c>
+      <c r="F29" s="14">
+        <v>100</v>
+      </c>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="14">
+        <v>180</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1115</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>325</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12628332.xlsx
+++ b/12628332.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0681A4-0A1B-4129-91C5-B2F41D90240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DB9EBC-C5D5-4AA0-832C-DA08CCBF530E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>it was a average day</t>
+  </si>
+  <si>
+    <t>2026/25/09</t>
   </si>
 </sst>
 </file>
@@ -2217,26 +2220,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="14">
+        <v>460</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
+        <v>150</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>160</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
